--- a/public/templates/000_pm_suite/01_프로젝트 관리/03_일정관리/프로젝트명_WBS_V1.0_20220531.xlsx
+++ b/public/templates/000_pm_suite/01_프로젝트 관리/03_일정관리/프로젝트명_WBS_V1.0_20220531.xlsx
@@ -33,7 +33,7 @@
     <t>추석</t>
   </si>
   <si>
-    <t>SyncGuard AI 시스템 구축</t>
+    <t>SyncFlow AI 시스템 구축</t>
   </si>
   <si>
     <t>개천절 대체공휴일</t>
@@ -42,7 +42,7 @@
     <t>한글날</t>
   </si>
   <si>
-    <t>한빛글로벌 SyncGuard AI 시스템 구축 작업분할구조도 (WBS)</t>
+    <t>한빛글로벌 SyncFlow AI 시스템 구축 작업분할구조도 (WBS)</t>
   </si>
   <si>
     <t>성탄절</t>
@@ -162,7 +162,7 @@
     <t>전체 계획 1.0% / 실적 1.2% (분석 단계: 계획 10.0% / 실적 12.0%)</t>
   </si>
   <si>
-    <t>10/16 착수 킥오프 회의 합의사항 반영 (마케팅허브 연계, 데이터브릿지 3M 투입, 골든셋 단계적 구축)</t>
+    <t>10/16 착수 킥오프 회의 합의사항 반영 (전자구매포털 연계, 데이터브릿지 3M 투입, 골든셋 단계적 구축)</t>
   </si>
   <si>
     <t>박준혁 AA / 김태윤 PM</t>
@@ -171,10 +171,10 @@
     <t>정민수 PM / 한승우 PM</t>
   </si>
   <si>
-    <t>한빛글로벌 SyncGuard AI</t>
+    <t>한빛글로벌 SyncFlow AI</t>
   </si>
   <si>
-    <t>한빛글로벌 SyncGuard AI 시스템 구축</t>
+    <t>한빛글로벌 SyncFlow AI 시스템 구축</t>
   </si>
   <si>
     <t>v1.1</t>
@@ -186,13 +186,13 @@
     <t>PoC/진척 반영</t>
   </si>
   <si>
-    <t>제1차 주간보고 기준 진척률(전체 계획 1.0%/실적 1.2%, 분석 계획 10.0%/실적 12.0%) 및 동영상 캡처·목업 PoC 반영</t>
+    <t>제1차 주간보고 기준 진척률(전체 계획 1.0%/실적 1.2%, 분석 계획 10.0%/실적 12.0%) 및 동도면 스냅샷·목업 PoC 반영</t>
   </si>
   <si>
     <t>김태윤 PM / 박준혁 AA</t>
   </si>
   <si>
-    <t>정민수 PM / RA Lab</t>
+    <t>정민수 PM / 품질법무검증팀</t>
   </si>
   <si>
     <t>최종작성일</t>
@@ -304,25 +304,25 @@
     <t>착수회의록(EMP_MAN_020), WBS, 사내계정</t>
   </si>
   <si>
-    <t>현행 심의 절차 인터뷰(RA 4인 전원) 및 기준자료 정제</t>
+    <t>현행 검증 절차 인터뷰(QA 4인 전원) 및 기준자료 정제</t>
   </si>
   <si>
-    <t>AI 아키텍트 / RA 4인</t>
+    <t>AI 아키텍트 / QA 4인</t>
   </si>
   <si>
     <t>사내 기준 단일포맷 정제본, 인터뷰록</t>
   </si>
   <si>
-    <t>동영상(사용자 지정 장면 캡처), 긴 JPG PoC 및 목업 검증</t>
+    <t>설계도면(사용자 지정 장면 스냅샷), 긴 JPG PoC 및 목업 검증</t>
   </si>
   <si>
     <t>박준혁 AA / 데이터브릿지</t>
   </si>
   <si>
-    <t>동영상 장면캡처 PoC, 마케팅허브·프로덕트랩 목업</t>
+    <t>설계도면 장면스냅샷 PoC, 전자구매포털·피엘엠넥서스 목업</t>
   </si>
   <si>
-    <t>KT레몬 vs 상용 LLM(Claude) 보고서 파싱 비교 및 요구사항 확정</t>
+    <t>HB-Monitor vs 상용 LLM(Claude) 보고서 파싱 비교 및 요구사항 확정</t>
   </si>
   <si>
     <t>사업총괄(PM) / 박준혁 AA</t>
@@ -337,25 +337,25 @@
     <t>[02] 화면·DB·IA·연계 상세 설계</t>
   </si>
   <si>
-    <t>마케팅허브 중심 의뢰/결과 동선 및 Side-by-Side 대조 뷰어 설계</t>
+    <t>전자구매포털 중심 의뢰/결과 동선 및 Side-by-Side 대조 뷰어 설계</t>
   </si>
   <si>
     <t>프론트엔드 개발자</t>
   </si>
   <si>
-    <t>화면설계서(대조뷰어·동영상캡처·관리자웹)</t>
+    <t>화면설계서(대조뷰어·동도면스냅샷·관리자웹)</t>
   </si>
   <si>
-    <t>PostgreSQL 16 + pgvector 통합 스키마 및 실증 DB ERD 설계</t>
+    <t>PostgreSQL 16 + pgvector 통합 스키마 및 시험검증 DB ERD 설계</t>
   </si>
   <si>
     <t>백엔드 / 데이터브릿지</t>
   </si>
   <si>
-    <t>데이터베이스명세서, ERD (마케팅허브 RDB·ProductLab)</t>
+    <t>데이터베이스명세서, ERD (전자구매포털 RDB·PLM-Nexus)</t>
   </si>
   <si>
-    <t>마케팅허브 REST API·뷰어 링크, ProductLab 배치, HB-SSO IAM 설계</t>
+    <t>전자구매포털 REST API·뷰어 링크, PLM-Nexus 배치, HB-SSO IAM 설계</t>
   </si>
   <si>
     <t>인터페이스설계서, 배치설계서 (데이터브릿지 11월 투입)</t>
@@ -382,7 +382,7 @@
     <t>[03] 규칙 사전·근거 검색·Agent 구축</t>
   </si>
   <si>
-    <t>식약처 표시·광고 공정화법·가이드라인 규제 문서 청킹 및 pgvector 적재</t>
+    <t>공정위·표준원 하도급거래 공정화법·가이드라인 규제 문서 청킹 및 pgvector 적재</t>
   </si>
   <si>
     <t>AI 엔지니어</t>
@@ -391,7 +391,7 @@
     <t>규제문서 수집목록, pgvector 임베딩 DB</t>
   </si>
   <si>
-    <t>사내 심의 기준(질문/답변 분리 엑셀) 기반 표현 사전(100대 규칙) 개발</t>
+    <t>사내 검증 기준(질문/답변 분리 엑셀) 기반 표현 사전(100대 규칙) 개발</t>
   </si>
   <si>
     <t>표현사전(금지/주의/안전) 100대 룰 엔진</t>
@@ -406,43 +406,43 @@
     <t>[04] 3단계 판정 엔진·프롬프트 개발 (M2)</t>
   </si>
   <si>
-    <t>PDF/PPT/JPG/동영상(지정 캡처 장면) 파싱 및 3단계 판정·대체문구 개발</t>
+    <t>PDF/PPT/JPG/설계도면(지정 도면 스냅샷) 파싱 및 3단계 판정·표준수정조항 개발</t>
   </si>
   <si>
-    <t>★M2 중간보고 프로토타입 (국·영문 번역심의 포함)</t>
+    <t>★M2 중간보고 프로토타입 (국·영문 번역검증 포함)</t>
   </si>
   <si>
     <t>판정 하향 금지 가드레일 및 법적 근거 부재 시 판정 유보 안전망 개발</t>
   </si>
   <si>
-    <t>판정 하향 금지 및 실증 필요 여부 분석 모듈</t>
+    <t>판정 하향 금지 및 시험검증 필요 여부 분석 모듈</t>
   </si>
   <si>
     <t>[05] 대조 뷰어·관리자 화면 및 결과 파일 고도화</t>
   </si>
   <si>
-    <t>Side-by-Side 시안 대조 뷰어(장면 이미지·문구 번호 클릭 연동) 개발</t>
+    <t>Side-by-Side 계약·도서 대조 뷰어(장면 이미지·조항 번호 클릭 연동) 개발</t>
   </si>
   <si>
-    <t>시안 대조 뷰어 및 동영상 장면 캡처 워크벤치</t>
+    <t>계약·도서 대조 뷰어 및 설계도면 스냅샷 추출 워크벤치</t>
   </si>
   <si>
-    <t>RA 최종 판정(반영/확정) 피드백 UI 및 표현사전·규제문서 관리자 웹 개발</t>
+    <t>QA 최종 판정(반영/확정) 피드백 UI 및 표현사전·규제문서 관리자 웹 개발</t>
   </si>
   <si>
-    <t>RA 관리자 사이트(표현사전·규제문서 버전관리)</t>
+    <t>QA 관리자 사이트(표현사전·규제문서 버전관리)</t>
   </si>
   <si>
-    <t>심의 결과 리포트 파일(실증자료 연결 포함 Word/PDF/Excel) 고도화</t>
+    <t>검증 결과 리포트 파일(시험성적서 연결 포함 Word/PDF/Excel) 고도화</t>
   </si>
   <si>
     <t>백엔드 개발자</t>
   </si>
   <si>
-    <t>심의결과 리포트 고도화 출력 모듈</t>
+    <t>검증결과 리포트 고도화 출력 모듈</t>
   </si>
   <si>
-    <t>[06] 마케팅허브·HB-SSO IAM·KT레몬 연계 개발 (M4)</t>
+    <t>[06] 전자구매포털·HB-SSO IAM·HB-Monitor 연계 개발 (M4)</t>
   </si>
   <si>
     <t>사내 HB-SSO IAM(SSO) 자동 로그인 및 관리자 웹 접근 연동</t>
@@ -451,37 +451,37 @@
     <t>HB-SSO IAM 통합 인증 연동 모듈</t>
   </si>
   <si>
-    <t>마케팅허브(MarketingHub) 심의 의뢰 수신·결과 회신 REST API 및 뷰어 링크 연동</t>
+    <t>전자구매포털(SRM-Portal) 검증 요청 수신·결과 회신 REST API 및 뷰어 링크 연동</t>
   </si>
   <si>
-    <t>★M4 마케팅허브 API 및 대조 뷰어 딥링크 연동 완료</t>
+    <t>★M4 전자구매포털 API 및 대조 뷰어 딥링크 연동 완료</t>
   </si>
   <si>
-    <t>마케팅허브 RDB 성분 기준 연동 및 보고서 파싱(LLM/KT레몬) 파이프라인 구축</t>
+    <t>전자구매포털 RDB 성분 기준 연동 및 보고서 파싱(LLM/HB-Monitor) 파이프라인 구축</t>
   </si>
   <si>
     <t>백엔드 / AI</t>
   </si>
   <si>
-    <t>마케팅허브 성분 RDB 및 실증보고서 매칭 모듈</t>
+    <t>전자구매포털 성분 RDB 및 시험검증보고서 매칭 모듈</t>
   </si>
   <si>
-    <t>[07] ProductLab 실증자료 DB 구축·연동 (M3)</t>
+    <t>[07] PLM-Nexus 시험성적서 DB 구축·연동 (M3)</t>
   </si>
   <si>
-    <t>ProductLab 원료 배합·세포효능 데이터 수집 배치 및 실증 DB 구축</t>
+    <t>PLM-Nexus 원소재 조성·배상한도성능규격 데이터 수집 배치 및 시험검증 DB 구축</t>
   </si>
   <si>
     <t>데이터브릿지 / 백엔드</t>
   </si>
   <si>
-    <t>ProductLab 원료·세포효능 실증 DB 구축</t>
+    <t>PLM-Nexus 원소재·배상한도성능규격 시험검증 DB 구축</t>
   </si>
   <si>
-    <t>기술원 인체적용시험·HUT 설문 보고서 및 첨부파일 DB 연동 완료 (M3)</t>
+    <t>기술원 공인신뢰성시험·HUT 설문 보고서 및 첨부파일 DB 연동 완료 (M3)</t>
   </si>
   <si>
-    <t>★M3 기술원 실증 보고서 연동 완료 (1월말 중간보고)</t>
+    <t>★M3 기술원 시험검증 보고서 연동 완료 (1월말 중간보고)</t>
   </si>
   <si>
     <t>시험 및 검증</t>
@@ -490,7 +490,7 @@
     <t>[08] 통합·연계·보안·성능 시험</t>
   </si>
   <si>
-    <t>마케팅허브·프로덕트랩·SyncGuard AI 전 구간 End-to-End 통합 테스트</t>
+    <t>전자구매포털·피엘엠넥서스·SyncFlow AI 전 구간 End-to-End 통합 테스트</t>
   </si>
   <si>
     <t>QA 리드 / 데이터브릿지</t>
@@ -523,13 +523,13 @@
     <t>프롬프트·규칙사전 파인튜닝 결과서</t>
   </si>
   <si>
-    <t>[10] 마케터·RA 현업 파일럿 및 골든셋 확장 (M5)</t>
+    <t>[10] 구매담당자·QA 현업 파일럿 및 골든셋 확장 (M5)</t>
   </si>
   <si>
-    <t>현업(마케터·RA) 시범운영 및 화면 '반영/확정' 이력 골든셋 자동 축적</t>
+    <t>현업(구매담당자·QA) 시범운영 및 화면 '반영/확정' 이력 골든셋 자동 축적</t>
   </si>
   <si>
-    <t>한빛글로벌 RA / 수행사</t>
+    <t>한빛글로벌 QA / 수행사</t>
   </si>
   <si>
     <t>현업 파일럿 운영일지 및 축적 골든셋 DB</t>
@@ -547,7 +547,7 @@
     <t>[11] 시스템 안정화·교육·검수 및 그랜드 오픈</t>
   </si>
   <si>
-    <t>마케터·RA 사용자 매뉴얼/운영자 가이드 제작 및 전사 교육</t>
+    <t>구매담당자·QA 사용자 매뉴얼/운영자 가이드 제작 및 전사 교육</t>
   </si>
   <si>
     <t>프론트엔드 / PM</t>
@@ -562,7 +562,7 @@
     <t>운영 환경 이관 확인서</t>
   </si>
   <si>
-    <t>최종 검수, 완료보고회 개최 및 SyncGuard AI 그랜드 오픈 (2027.05.31)</t>
+    <t>최종 검수, 완료보고회 개최 및 SyncFlow AI 그랜드 오픈 (2027.05.31)</t>
   </si>
   <si>
     <t>양사 PM / 전원</t>
@@ -17132,7 +17132,7 @@
         <f>DATE(2027,2,22)</f>
         <v>46440</v>
       </c>
-      <c r="AP2" s="63">
+      <c r="HB2" s="63">
         <f>DATE(2027,3,1)</f>
         <v>46447</v>
       </c>
@@ -17261,7 +17261,7 @@
       <c r="AM3" s="91"/>
       <c r="AN3" s="91"/>
       <c r="AO3" s="91"/>
-      <c r="AP3" s="91"/>
+      <c r="HB3" s="91"/>
       <c r="AQ3" s="91"/>
       <c r="AR3" s="91"/>
       <c r="AS3" s="91"/>
@@ -17336,7 +17336,7 @@
       <c r="AM4" s="103"/>
       <c r="AN4" s="103"/>
       <c r="AO4" s="104"/>
-      <c r="AP4" s="102">
+      <c r="HB4" s="102">
         <v>46447.0</v>
       </c>
       <c r="AQ4" s="103"/>
@@ -17499,7 +17499,7 @@
         <f>"2월 4W(M4)"&amp;IF(AND(DATE(2027,2,22)&lt;=IF(ISBLANK($K$1), TODAY(), $K$1), IF(ISBLANK($K$1), TODAY(), $K$1)&lt;DATE(2027,3,1)), "★", "")</f>
         <v>2월 4W(M4)</v>
       </c>
-      <c r="AP5" s="115" t="str">
+      <c r="HB5" s="115" t="str">
         <f>"3월 1W"&amp;IF(AND(DATE(2027,3,1)&lt;=IF(ISBLANK($K$1), TODAY(), $K$1), IF(ISBLANK($K$1), TODAY(), $K$1)&lt;DATE(2027,3,8)), "★", "")</f>
         <v>3월 1W</v>
       </c>
@@ -17701,7 +17701,7 @@
         <f t="shared" si="4"/>
         <v/>
       </c>
-      <c r="AP6" s="135" t="str">
+      <c r="HB6" s="135" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
@@ -17895,7 +17895,7 @@
         <f t="shared" si="7"/>
         <v/>
       </c>
-      <c r="AP7" s="135" t="str">
+      <c r="HB7" s="135" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
@@ -18089,7 +18089,7 @@
         <f t="shared" si="9"/>
         <v/>
       </c>
-      <c r="AP8" s="135" t="str">
+      <c r="HB8" s="135" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
@@ -18283,7 +18283,7 @@
         <f t="shared" si="11"/>
         <v/>
       </c>
-      <c r="AP9" s="135" t="str">
+      <c r="HB9" s="135" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
@@ -18481,7 +18481,7 @@
         <f t="shared" si="13"/>
         <v/>
       </c>
-      <c r="AP10" s="135" t="str">
+      <c r="HB10" s="135" t="str">
         <f t="shared" si="13"/>
         <v/>
       </c>
@@ -18671,7 +18671,7 @@
         <f t="shared" si="15"/>
         <v/>
       </c>
-      <c r="AP11" s="135" t="str">
+      <c r="HB11" s="135" t="str">
         <f t="shared" si="15"/>
         <v/>
       </c>
@@ -18861,7 +18861,7 @@
         <f t="shared" si="17"/>
         <v/>
       </c>
-      <c r="AP12" s="135" t="str">
+      <c r="HB12" s="135" t="str">
         <f t="shared" si="17"/>
         <v/>
       </c>
@@ -19051,7 +19051,7 @@
         <f t="shared" si="19"/>
         <v/>
       </c>
-      <c r="AP13" s="135" t="str">
+      <c r="HB13" s="135" t="str">
         <f t="shared" si="19"/>
         <v/>
       </c>
@@ -19241,7 +19241,7 @@
         <f t="shared" si="21"/>
         <v/>
       </c>
-      <c r="AP14" s="135" t="str">
+      <c r="HB14" s="135" t="str">
         <f t="shared" si="21"/>
         <v/>
       </c>
@@ -19439,7 +19439,7 @@
         <f t="shared" si="23"/>
         <v/>
       </c>
-      <c r="AP15" s="135" t="str">
+      <c r="HB15" s="135" t="str">
         <f t="shared" si="23"/>
         <v/>
       </c>
@@ -19629,7 +19629,7 @@
         <f t="shared" si="25"/>
         <v/>
       </c>
-      <c r="AP16" s="135" t="str">
+      <c r="HB16" s="135" t="str">
         <f t="shared" si="25"/>
         <v/>
       </c>
@@ -19819,7 +19819,7 @@
         <f t="shared" si="28"/>
         <v/>
       </c>
-      <c r="AP17" s="135" t="str">
+      <c r="HB17" s="135" t="str">
         <f t="shared" si="28"/>
         <v/>
       </c>
@@ -20011,7 +20011,7 @@
         <f t="shared" si="30"/>
         <v/>
       </c>
-      <c r="AP18" s="135" t="str">
+      <c r="HB18" s="135" t="str">
         <f t="shared" si="30"/>
         <v/>
       </c>
@@ -20201,7 +20201,7 @@
         <f t="shared" si="32"/>
         <v/>
       </c>
-      <c r="AP19" s="147" t="str">
+      <c r="HB19" s="147" t="str">
         <f t="shared" si="32"/>
         <v/>
       </c>
@@ -20393,7 +20393,7 @@
         <f t="shared" si="34"/>
         <v/>
       </c>
-      <c r="AP20" s="135" t="str">
+      <c r="HB20" s="135" t="str">
         <f t="shared" si="34"/>
         <v/>
       </c>
@@ -20583,7 +20583,7 @@
         <f t="shared" si="36"/>
         <v/>
       </c>
-      <c r="AP21" s="135" t="str">
+      <c r="HB21" s="135" t="str">
         <f t="shared" si="36"/>
         <v/>
       </c>
@@ -20773,7 +20773,7 @@
         <f t="shared" si="38"/>
         <v/>
       </c>
-      <c r="AP22" s="135" t="str">
+      <c r="HB22" s="135" t="str">
         <f t="shared" si="38"/>
         <v/>
       </c>
@@ -20965,7 +20965,7 @@
         <f t="shared" si="40"/>
         <v/>
       </c>
-      <c r="AP23" s="135" t="str">
+      <c r="HB23" s="135" t="str">
         <f t="shared" si="40"/>
         <v/>
       </c>
@@ -21155,7 +21155,7 @@
         <f t="shared" si="42"/>
         <v>M4</v>
       </c>
-      <c r="AP24" s="135" t="str">
+      <c r="HB24" s="135" t="str">
         <f t="shared" si="42"/>
         <v/>
       </c>
@@ -21345,7 +21345,7 @@
         <f t="shared" si="44"/>
         <v/>
       </c>
-      <c r="AP25" s="135" t="str">
+      <c r="HB25" s="135" t="str">
         <f t="shared" si="44"/>
         <v/>
       </c>
@@ -21537,7 +21537,7 @@
         <f t="shared" si="46"/>
         <v/>
       </c>
-      <c r="AP26" s="135" t="str">
+      <c r="HB26" s="135" t="str">
         <f t="shared" si="46"/>
         <v/>
       </c>
@@ -21727,7 +21727,7 @@
         <f t="shared" si="48"/>
         <v/>
       </c>
-      <c r="AP27" s="135" t="str">
+      <c r="HB27" s="135" t="str">
         <f t="shared" si="48"/>
         <v/>
       </c>
@@ -21925,7 +21925,7 @@
         <f t="shared" si="50"/>
         <v/>
       </c>
-      <c r="AP28" s="142" t="str">
+      <c r="HB28" s="142" t="str">
         <f t="shared" si="50"/>
         <v/>
       </c>
@@ -22115,7 +22115,7 @@
         <f t="shared" si="52"/>
         <v/>
       </c>
-      <c r="AP29" s="135" t="str">
+      <c r="HB29" s="135" t="str">
         <f t="shared" si="52"/>
         <v/>
       </c>
@@ -22307,7 +22307,7 @@
         <f t="shared" si="54"/>
         <v/>
       </c>
-      <c r="AP30" s="135" t="str">
+      <c r="HB30" s="135" t="str">
         <f t="shared" si="54"/>
         <v/>
       </c>
@@ -22497,7 +22497,7 @@
         <f t="shared" si="56"/>
         <v/>
       </c>
-      <c r="AP31" s="135" t="str">
+      <c r="HB31" s="135" t="str">
         <f t="shared" si="56"/>
         <v/>
       </c>
@@ -22689,7 +22689,7 @@
         <f t="shared" si="58"/>
         <v/>
       </c>
-      <c r="AP32" s="135" t="str">
+      <c r="HB32" s="135" t="str">
         <f t="shared" si="58"/>
         <v/>
       </c>
@@ -22879,7 +22879,7 @@
         <f t="shared" si="60"/>
         <v/>
       </c>
-      <c r="AP33" s="147" t="str">
+      <c r="HB33" s="147" t="str">
         <f t="shared" si="60"/>
         <v/>
       </c>
@@ -23077,7 +23077,7 @@
         <f t="shared" si="62"/>
         <v/>
       </c>
-      <c r="AP34" s="135" t="str">
+      <c r="HB34" s="135" t="str">
         <f t="shared" si="62"/>
         <v/>
       </c>
@@ -23267,7 +23267,7 @@
         <f t="shared" si="64"/>
         <v/>
       </c>
-      <c r="AP35" s="135" t="str">
+      <c r="HB35" s="135" t="str">
         <f t="shared" si="64"/>
         <v/>
       </c>
@@ -23457,7 +23457,7 @@
         <f t="shared" si="66"/>
         <v/>
       </c>
-      <c r="AP36" s="170" t="str">
+      <c r="HB36" s="170" t="str">
         <f t="shared" si="66"/>
         <v/>
       </c>
@@ -23577,7 +23577,7 @@
       <c r="AM37" s="183"/>
       <c r="AN37" s="183"/>
       <c r="AO37" s="184"/>
-      <c r="AP37" s="182"/>
+      <c r="HB37" s="182"/>
       <c r="AQ37" s="183"/>
       <c r="AR37" s="183"/>
       <c r="AS37" s="183"/>
@@ -26403,7 +26403,7 @@
     <mergeCell ref="AC4:AG4"/>
     <mergeCell ref="AH4:AK4"/>
     <mergeCell ref="AL4:AO4"/>
-    <mergeCell ref="AP4:AT4"/>
+    <mergeCell ref="HB4:AT4"/>
     <mergeCell ref="AU4:AX4"/>
     <mergeCell ref="AY4:BB4"/>
     <mergeCell ref="O3:O4"/>
